--- a/Result/profitability/2637.xlsx
+++ b/Result/profitability/2637.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>4.08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.8425</v>
+        <v>1.8925</v>
       </c>
       <c r="N2" t="n">
-        <v>28.85375</v>
+        <v>29.16375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.75125</v>
+        <v>1.85</v>
       </c>
       <c r="N3" t="n">
-        <v>29.235</v>
+        <v>30.61125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>4.05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.045</v>
+        <v>2.38625</v>
       </c>
       <c r="N4" t="n">
-        <v>30.4375</v>
+        <v>34.48875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>98.09999999999999</v>
@@ -1018,10 +1018,10 @@
         <v>1.34</v>
       </c>
       <c r="M5" t="n">
-        <v>2.2425</v>
+        <v>2.47625</v>
       </c>
       <c r="N5" t="n">
-        <v>33.8125</v>
+        <v>36.4525</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3425</v>
+        <v>2.39625</v>
       </c>
       <c r="N6" t="n">
-        <v>35.9175</v>
+        <v>36.97625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.99</v>
       </c>
       <c r="M7" t="n">
-        <v>2.33375</v>
+        <v>2.29125</v>
       </c>
       <c r="N7" t="n">
-        <v>35.74</v>
+        <v>35.91500000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>2.02</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2325</v>
+        <v>2.34375</v>
       </c>
       <c r="N8" t="n">
-        <v>34.8425</v>
+        <v>36.15375</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>1.67625</v>
       </c>
       <c r="N10" t="n">
-        <v>34.69625</v>
+        <v>34.69625000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -9576,6 +9576,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2637</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>5342</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3249</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2093</v>
+      </c>
+      <c r="F73" t="n">
+        <v>39.17</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2032</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>38.04%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>-165</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1867</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1862</v>
+      </c>
+      <c r="L73" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.64375</v>
+      </c>
+      <c r="N73" t="n">
+        <v>28.2475</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.8900000000000001</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.5562500000000001</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.3657601115760112</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>3.016129032258065</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>1.170083102493075</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
